--- a/mlef_pipeline/results/OS_6/IO_ONLY/RWD/results.xlsx
+++ b/mlef_pipeline/results/OS_6/IO_ONLY/RWD/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.70 ± 0.03</t>
+          <t>0.71 ± 0.03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.63 ± 0.04</t>
+          <t>0.64 ± 0.03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.63 ± 0.07</t>
+          <t>0.63 ± 0.05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.65 ± 0.11</t>
+          <t>0.69 ± 0.09</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -503,12 +503,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -528,12 +528,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.63 ± 0.13</t>
+          <t>0.65 ± 0.13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F4" t="n">
